--- a/assets/Tableau-Synthese-Mergim.xlsx
+++ b/assets/Tableau-Synthese-Mergim.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PORTFOLIO\html5up-astral\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1AB07C-4005-4FB0-B265-4B34CB5B8119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C794E-3CFD-40E5-9083-A4A191957A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,9 +110,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
-  </si>
-  <si>
     <t>SESSION 2025</t>
   </si>
   <si>
@@ -255,6 +252,9 @@
   </si>
   <si>
     <t>14/04/2025 au 10/06/2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://mergim-it.github.io/Portfolio/</t>
   </si>
 </sst>
 </file>
@@ -737,9 +737,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -762,45 +801,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1122,56 +1122,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="19"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="38"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="23"/>
+      <c r="A4" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1183,22 +1183,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="A5" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1221,8 +1221,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1278,16 +1278,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="30"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1326,18 +1326,18 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="13">
         <v>45557</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="12"/>
@@ -1379,21 +1379,21 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="13">
         <v>45582</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10"/>
@@ -1434,22 +1434,22 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="14">
         <v>45665</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1489,22 +1489,22 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="14">
         <v>45915</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -1544,16 +1544,16 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="14">
         <v>46012</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
@@ -1597,19 +1597,19 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="14">
         <v>45933</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14"/>
@@ -1650,19 +1650,19 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="14">
         <v>45979</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15"/>
@@ -1703,21 +1703,21 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="14">
         <v>45940</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16"/>
@@ -1758,19 +1758,19 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="14">
         <v>45975</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17"/>
@@ -1811,20 +1811,20 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>69</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>70</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -1863,16 +1863,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="25"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1911,21 +1911,21 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20"/>
@@ -1966,14 +1966,14 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
@@ -2017,16 +2017,16 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
@@ -2070,21 +2070,21 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23"/>
@@ -2125,14 +2125,14 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
@@ -2176,21 +2176,21 @@
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25"/>
@@ -2231,13 +2231,13 @@
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
@@ -2281,16 +2281,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="25"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2329,18 +2329,18 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="C28" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>46</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G28" s="11"/>
       <c r="H28" s="12"/>
@@ -2382,20 +2382,20 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="C29" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -2435,21 +2435,21 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="C30" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30"/>
@@ -2490,19 +2490,19 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>52</v>
-      </c>
       <c r="C31" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31"/>
@@ -2543,14 +2543,14 @@
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>54</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
@@ -2594,17 +2594,17 @@
     </row>
     <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33"/>
@@ -2645,19 +2645,19 @@
     </row>
     <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>57</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34"/>
@@ -2698,13 +2698,13 @@
     </row>
     <row r="35" spans="1:43" s="2" customFormat="1" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
@@ -2749,38 +2749,38 @@
     </row>
     <row r="36" spans="1:43" customFormat="1" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="16" t="s">
         <v>59</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>60</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H36" s="12"/>
     </row>
     <row r="37" spans="1:43" customFormat="1" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="16" t="s">
         <v>61</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2829,6 +2829,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2836,11 +2841,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
